--- a/artfynd/A 4532-2025 artfynd.xlsx
+++ b/artfynd/A 4532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121062580</v>
+        <v>96850663</v>
       </c>
       <c r="B2" t="n">
-        <v>42961</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -723,19 +718,16 @@
           <t>larv/nymf</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hygge syd om Västerbacken, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>694323</v>
+        <v>694316</v>
       </c>
       <c r="R2" t="n">
-        <v>6659933</v>
+        <v>6659973</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,17 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 m upp.</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +768,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -803,15 +789,2513 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>96850664</v>
+      </c>
+      <c r="B3" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>694313</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6659964</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>96850666</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>694322</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6659962</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96850667</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>694324</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6659960</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96850669</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>694324</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6659961</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96850670</v>
+      </c>
+      <c r="B7" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>694330</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6659956</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96850671</v>
+      </c>
+      <c r="B8" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>694350</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6659959</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96850673</v>
+      </c>
+      <c r="B9" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>694338</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6659959</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>96850674</v>
+      </c>
+      <c r="B10" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>694341</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6659963</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>96850676</v>
+      </c>
+      <c r="B11" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>694342</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6659964</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>96850702</v>
+      </c>
+      <c r="B12" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>694382</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6659984</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg, Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>105040800</v>
+      </c>
+      <c r="B13" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hygge syd om västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>694315</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6659980</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>105040801</v>
+      </c>
+      <c r="B14" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hygge syd om västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>694314</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6659962</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>105040897</v>
+      </c>
+      <c r="B15" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hygge syd om västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>694320</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6659961</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>105040898</v>
+      </c>
+      <c r="B16" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hygge syd om västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>694325</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6659961</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>105041039</v>
+      </c>
+      <c r="B17" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hygge syd om västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>694315</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6659974</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>111675761</v>
+      </c>
+      <c r="B18" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norrtälje kommun, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>694315</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6659972</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg, Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>111675763</v>
+      </c>
+      <c r="B19" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norrtälje kommun, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>694321</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6659965</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg, Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121062580</v>
+      </c>
+      <c r="B20" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>694323</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6659933</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2 m upp.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Ward Tamsyn</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Ward Tamsyn, Tore Dahlberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asknätfjäril i AB län </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121062581</v>
+      </c>
+      <c r="B21" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>694320</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6659954</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>3 m upp.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
         <is>
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>

--- a/artfynd/A 4532-2025 artfynd.xlsx
+++ b/artfynd/A 4532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850663</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -932,6 +942,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850664</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1062,6 +1077,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850666</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1192,6 +1212,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850667</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1322,6 +1347,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850669</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1452,6 +1482,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850670</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1582,6 +1617,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850671</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1712,6 +1752,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850673</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1842,6 +1887,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850674</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1972,6 +2022,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850676</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2102,6 +2157,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850702</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2236,6 +2296,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040800</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2370,6 +2435,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040801</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2504,6 +2574,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040897</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2638,6 +2713,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040898</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2772,6 +2852,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105041039</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2897,6 +2982,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111675761</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3022,6 +3112,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111675763</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3161,6 +3256,11 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062580</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3300,8 +3400,35 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062581</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>